--- a/www/download/IND.surplus_value.empe_hs.r.pc.rpA2.xlsx
+++ b/www/download/IND.surplus_value.empe_hs.r.pc.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>263.48</t>
+          <t>2.63477665737722</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>244.11</t>
+          <t>2.44110774072085</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>253.68</t>
+          <t>2.53682763215396</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>250.49</t>
+          <t>2.50487362384055</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>225.58</t>
+          <t>2.25575954374296</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>236.73</t>
+          <t>2.36727741140907</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>239.38</t>
+          <t>2.39376094247614</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>224.72</t>
+          <t>2.24718524834654</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>205.11</t>
+          <t>2.05110931669699</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>162.45</t>
+          <t>1.62451673065952</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>147.68</t>
+          <t>1.47675522566286</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>153.15</t>
+          <t>1.53153038857354</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>1.48996228245679</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>168.03</t>
+          <t>1.68033820569919</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>176.72</t>
+          <t>1.7672368057993</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>93.77</t>
+          <t>0.937719831166887</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>97.43</t>
+          <t>0.974263410642285</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>133.6</t>
+          <t>1.33600795570445</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>131.6</t>
+          <t>1.31598676684208</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>131.46</t>
+          <t>1.31455077538373</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>144.28</t>
+          <t>1.44275697481087</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>141.65</t>
+          <t>1.41649046888843</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>135.55</t>
+          <t>1.35545634499223</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>126.88</t>
+          <t>1.26876570267924</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>108.55</t>
+          <t>1.08552809765914</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>1.07497781888295</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>103.03</t>
+          <t>1.03031772129847</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>101.78</t>
+          <t>1.01776893675767</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>105.01</t>
+          <t>1.05006555510972</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>116.97</t>
+          <t>1.16974375326944</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>0.729075326433899</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>68.67</t>
+          <t>0.686735810008864</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>0.788710055177574</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>78.71</t>
+          <t>0.787082943969255</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>63.21</t>
+          <t>0.632142960087497</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>58.62</t>
+          <t>0.586236734390419</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>48.77</t>
+          <t>0.487699934914363</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>0.370557402576921</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>0.199283907833747</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>0.0584261047579637</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>0.0707716766304722</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0832848936407886</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>0.135150346281362</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>0.271980712616782</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>0.196128782685844</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>937.55</t>
+          <t>9.37550616853927</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1062.2</t>
+          <t>10.6219528279284</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1261.14</t>
+          <t>12.6113502931597</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>846.42</t>
+          <t>8.46416100737506</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>859.2</t>
+          <t>8.59202971228059</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>880.95</t>
+          <t>8.80950487660474</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>849.17</t>
+          <t>8.49169601482028</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>811.02</t>
+          <t>8.11017522525196</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1046.29</t>
+          <t>10.4628697500475</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>808.32</t>
+          <t>8.08324120766626</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>834.47</t>
+          <t>8.34466287321692</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>835.11</t>
+          <t>8.3510653446564</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>781.11</t>
+          <t>7.81105400805675</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>653.63</t>
+          <t>6.53628294401321</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>578.1</t>
+          <t>5.78103626143372</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>189.05</t>
+          <t>1.8904712464156</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>186.22</t>
+          <t>1.86217512751993</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>204.99</t>
+          <t>2.04994989574353</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>199.75</t>
+          <t>1.99754764722383</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>222.69</t>
+          <t>2.2269469242906</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>241.2</t>
+          <t>2.41198154831165</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>252.9</t>
+          <t>2.52904992169141</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>262.19</t>
+          <t>2.62186639074624</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>275.65</t>
+          <t>2.75649440314608</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>275.64</t>
+          <t>2.75637878948015</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>267.7</t>
+          <t>2.67701833981671</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>270.37</t>
+          <t>2.70366483536395</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>274.63</t>
+          <t>2.74633015450887</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>266.46</t>
+          <t>2.66460468392458</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>280.4</t>
+          <t>2.80401406324366</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>332.52</t>
+          <t>3.32524827856153</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>324.16</t>
+          <t>3.24158999564283</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>335.38</t>
+          <t>3.35378437118849</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>312.26</t>
+          <t>3.12262593151385</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>290.89</t>
+          <t>2.90886188840833</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>261.91</t>
+          <t>2.61907599303805</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>238.92</t>
+          <t>2.38922762804552</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>234.4</t>
+          <t>2.34398406722136</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>218.47</t>
+          <t>2.18466879193273</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>206.66</t>
+          <t>2.06659510348326</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>191.24</t>
+          <t>1.912390933761</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>181.18</t>
+          <t>1.8118245150071</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>193.05</t>
+          <t>1.93053074029023</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>195.36</t>
+          <t>1.95359127274544</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>220.66</t>
+          <t>2.2065734193723</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>154.18</t>
+          <t>1.54177606631902</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>164.87</t>
+          <t>1.64873713457998</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>150.84</t>
+          <t>1.50843137515946</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>141.97</t>
+          <t>1.41973336056473</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>136.09</t>
+          <t>1.36093956653386</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>140.09</t>
+          <t>1.40089934501679</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>157.17</t>
+          <t>1.57174321697475</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>165.5</t>
+          <t>1.65497259308275</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>172.81</t>
+          <t>1.72811508448333</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>193.48</t>
+          <t>1.93480380022341</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>202.04</t>
+          <t>2.02036714238735</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>195.97</t>
+          <t>1.95973357575408</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>221.97</t>
+          <t>2.2196662031013</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>212.95</t>
+          <t>2.12953169735983</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>218.59</t>
+          <t>2.18592660567526</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>276.55</t>
+          <t>2.76552879554064</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>276.87</t>
+          <t>2.76865874753448</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>326.95</t>
+          <t>3.26945959436028</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>300.94</t>
+          <t>3.00943974526618</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>272.31</t>
+          <t>2.72314512812701</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>273.91</t>
+          <t>2.73906137773621</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>256.83</t>
+          <t>2.56825862228624</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>2.43602628805659</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>213.4</t>
+          <t>2.13404622725498</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>204.7</t>
+          <t>2.04704918322284</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>211.28</t>
+          <t>2.11276730654041</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>218.47</t>
+          <t>2.18474342528898</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>248.17</t>
+          <t>2.48169599260734</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>209.28</t>
+          <t>2.09284279394946</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>264.06</t>
+          <t>2.64058650785804</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>632.31</t>
+          <t>6.32313432178225</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>413.63</t>
+          <t>4.13625134742159</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>451.32</t>
+          <t>4.51319931839016</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>446.91</t>
+          <t>4.46910990107412</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>449.54</t>
+          <t>4.49536445066818</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>468.94</t>
+          <t>4.68938230586798</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>416.39</t>
+          <t>4.1638636521383</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>393.8</t>
+          <t>3.93796727967838</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>401.28</t>
+          <t>4.01277320777355</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>328.38</t>
+          <t>3.28378546692468</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>313.83</t>
+          <t>3.13832260248666</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>324.61</t>
+          <t>3.24605210686081</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>317.97</t>
+          <t>3.17965097733705</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>338.94</t>
+          <t>3.38939123351223</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>389.22</t>
+          <t>3.89220243452668</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>89.75</t>
+          <t>0.897467953611551</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>103.36</t>
+          <t>1.03361990466554</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>127.38</t>
+          <t>1.27382102974805</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>120.8</t>
+          <t>1.20803313206082</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>117.65</t>
+          <t>1.17654262209657</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>107.59</t>
+          <t>1.07594301253671</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>110.96</t>
+          <t>1.10964549498394</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>104.2</t>
+          <t>1.04201669489696</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>0.797973098720595</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>80.13</t>
+          <t>0.801321138352967</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>86.05</t>
+          <t>0.860461776404146</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>80.82</t>
+          <t>0.808229569602605</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>76.81</t>
+          <t>0.768122144958874</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>0.852854925078645</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>90.07</t>
+          <t>0.90065231573066</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>126.08</t>
+          <t>1.26079293874031</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>129.28</t>
+          <t>1.29283551577984</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>186.65</t>
+          <t>1.86649830584443</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>165.67</t>
+          <t>1.65667372376074</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>1.62404777748676</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>169.59</t>
+          <t>1.6958722723801</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>156.28</t>
+          <t>1.56283698167874</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>144.62</t>
+          <t>1.44624570777439</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>113.54</t>
+          <t>1.13542851212212</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>110.05</t>
+          <t>1.10053324406004</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>114.42</t>
+          <t>1.14419725535567</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>113.81</t>
+          <t>1.13814356145721</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>112.25</t>
+          <t>1.1225166793448</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>123.76</t>
+          <t>1.23756764566684</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>141.29</t>
+          <t>1.41286548883676</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>215.59</t>
+          <t>2.15588670455661</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>227.88</t>
+          <t>2.27877138536383</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>2.85999611353177</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>256.27</t>
+          <t>2.56272789790551</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>238.46</t>
+          <t>2.38458170006332</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>255.77</t>
+          <t>2.55768662431295</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>236.49</t>
+          <t>2.36494676183423</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>218.06</t>
+          <t>2.18064915094188</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>210.55</t>
+          <t>2.10547793524791</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>180.39</t>
+          <t>1.80393232920579</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>180.03</t>
+          <t>1.80033424028035</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>177.24</t>
+          <t>1.7724351328452</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>178.97</t>
+          <t>1.78971559384342</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>182.27</t>
+          <t>1.82270045206692</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>208.58</t>
+          <t>2.08576017982858</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>5.44997700484698</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>523.62</t>
+          <t>5.23616046245464</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>520.64</t>
+          <t>5.20642100217528</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>486.32</t>
+          <t>4.86324418489825</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>469.72</t>
+          <t>4.69722394832282</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>404.31</t>
+          <t>4.04312178219932</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>433.38</t>
+          <t>4.33377671463696</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>337.67</t>
+          <t>3.37666520545883</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>297.5</t>
+          <t>2.97495589189446</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>270.14</t>
+          <t>2.70137627412802</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>306.42</t>
+          <t>3.06424347876715</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>320.4</t>
+          <t>3.204030620284</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>328.79</t>
+          <t>3.28785725506598</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>295.07</t>
+          <t>2.95065296189223</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>303.28</t>
+          <t>3.0328021180481</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>216.47</t>
+          <t>2.16465306727024</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>210.78</t>
+          <t>2.10781950277178</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>267.12</t>
+          <t>2.67122655583345</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>239.96</t>
+          <t>2.39959174908951</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>226.47</t>
+          <t>2.26474941365236</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>251.24</t>
+          <t>2.51239397822398</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>243.77</t>
+          <t>2.43770514437015</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>237.9</t>
+          <t>2.37896016551276</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>217.8</t>
+          <t>2.17798913160803</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>188.4</t>
+          <t>1.88404913983339</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>180.94</t>
+          <t>1.80936283058833</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>173.91</t>
+          <t>1.73908162817279</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>171.12</t>
+          <t>1.71117784028476</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>173.24</t>
+          <t>1.73244645441742</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>183.16</t>
+          <t>1.83163314148364</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>155.88</t>
+          <t>1.55879334277975</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>145.47</t>
+          <t>1.45471993753978</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>192.32</t>
+          <t>1.92315120111273</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>165.21</t>
+          <t>1.65212180893341</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>150.39</t>
+          <t>1.503890554251</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>147.32</t>
+          <t>1.47319588178453</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>133.71</t>
+          <t>1.33710445175834</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>123.32</t>
+          <t>1.23320698717446</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>121.61</t>
+          <t>1.21609460364018</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>104.22</t>
+          <t>1.04222569911678</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>106.41</t>
+          <t>1.0640818632013</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>113.48</t>
+          <t>1.13483188881181</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>114.84</t>
+          <t>1.14841223562658</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>119.74</t>
+          <t>1.19741607171814</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>133.53</t>
+          <t>1.33527921955029</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>248.59</t>
+          <t>2.48588980167109</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>235.39</t>
+          <t>2.35386625189373</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>258.26</t>
+          <t>2.58260771160763</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>226.69</t>
+          <t>2.26685930610053</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>211.59</t>
+          <t>2.11590768729931</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>196.77</t>
+          <t>1.96774964558204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>185.07</t>
+          <t>1.85074802159321</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>174.43</t>
+          <t>1.74433814347279</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>154.3</t>
+          <t>1.54300475124499</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>141.19</t>
+          <t>1.41189745853257</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>143.07</t>
+          <t>1.43071183506941</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>1.42302745385358</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>148.94</t>
+          <t>1.48938506815238</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>173.16</t>
+          <t>1.73159009016528</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>199.44</t>
+          <t>1.99436974856066</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>408.85</t>
+          <t>4.08850998753472</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>384.51</t>
+          <t>3.84512503472357</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>382.63</t>
+          <t>3.82626064684442</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>389.11</t>
+          <t>3.89113467125805</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>364.36</t>
+          <t>3.64364991838798</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>339.85</t>
+          <t>3.39852381137936</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>344.29</t>
+          <t>3.4428774237912</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>290.77</t>
+          <t>2.90773182299772</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>294.46</t>
+          <t>2.94462255056883</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>277.66</t>
+          <t>2.77659471393117</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>289.37</t>
+          <t>2.8936533702707</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>299.26</t>
+          <t>2.99256240337456</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>279.16</t>
+          <t>2.79164837162304</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>267.34</t>
+          <t>2.67339948354662</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>260.01</t>
+          <t>2.60010157316117</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>288.34</t>
+          <t>2.88337642894622</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>302.27</t>
+          <t>3.02268097827297</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>324.52</t>
+          <t>3.24516755589873</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>333.06</t>
+          <t>3.3306132019567</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>310.67</t>
+          <t>3.10670065690122</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>317.98</t>
+          <t>3.17975332041782</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>330.18</t>
+          <t>3.30176222833463</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>293.85</t>
+          <t>2.93849896963947</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>311.87</t>
+          <t>3.11871640476175</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>311.27</t>
+          <t>3.11274684423853</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>311.9</t>
+          <t>3.11904413605634</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>334.22</t>
+          <t>3.34216807403564</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>317.33</t>
+          <t>3.1732989816914</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>355.08</t>
+          <t>3.55077184212372</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>384.19</t>
+          <t>3.84185439558378</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>334.24</t>
+          <t>3.34239283702081</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>419.69</t>
+          <t>4.19693683563056</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>532.73</t>
+          <t>5.32728204152221</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>687.2</t>
+          <t>6.87202129904944</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>866.5</t>
+          <t>8.66503585393841</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>545.09</t>
+          <t>5.45091731745005</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>513.59</t>
+          <t>5.13591063620298</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>512.07</t>
+          <t>5.12067431786772</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>428.39</t>
+          <t>4.28392195813015</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>463.99</t>
+          <t>4.63988039614631</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>305.15</t>
+          <t>3.05152474303603</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>284.21</t>
+          <t>2.84209211387212</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>224.75</t>
+          <t>2.24752247037033</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>238.16</t>
+          <t>2.38158588857081</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>231.22</t>
+          <t>2.31224780391841</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>0.90406828537482</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>108.34</t>
+          <t>1.08335551048989</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>97.27</t>
+          <t>0.972730897406753</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>92.78</t>
+          <t>0.927782093500669</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>94.51</t>
+          <t>0.945076644209299</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>90.99</t>
+          <t>0.909905295799672</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>0.88459880161288</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>94.95</t>
+          <t>0.949501733854217</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>85.53</t>
+          <t>0.855260052591658</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>80.74</t>
+          <t>0.807428281355569</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>0.779977605629518</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>0.770019727607763</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>88.26</t>
+          <t>0.882563219213133</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>95.38</t>
+          <t>0.95383018044396</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>0.888085495327288</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>263.12</t>
+          <t>2.63118240604316</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>257.98</t>
+          <t>2.57977422616623</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>297.21</t>
+          <t>2.97214812195759</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>316.76</t>
+          <t>3.16758270817669</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>319.14</t>
+          <t>3.19139893928758</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>314.07</t>
+          <t>3.14074186531755</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>268.98</t>
+          <t>2.6897555773058</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>248.95</t>
+          <t>2.4894711543649</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>275.12</t>
+          <t>2.75118123917623</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>294.05</t>
+          <t>2.94054695167228</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>255.08</t>
+          <t>2.55082221355463</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>235.49</t>
+          <t>2.35494206984538</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>207.81</t>
+          <t>2.07807778261848</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>201.1</t>
+          <t>2.01095267112013</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>175.16</t>
+          <t>1.75164255471035</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>191.08</t>
+          <t>1.91075421840343</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>182.65</t>
+          <t>1.82653301324318</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>202.42</t>
+          <t>2.02415789515354</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>200.75</t>
+          <t>2.00745118255007</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>195.98</t>
+          <t>1.95977783411466</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>182.29</t>
+          <t>1.82291638900841</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>185.87</t>
+          <t>1.85874208836858</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>181.42</t>
+          <t>1.81423210345589</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>170.99</t>
+          <t>1.7098901389645</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>143.46</t>
+          <t>1.43455145026292</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>151.99</t>
+          <t>1.51992487280099</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>153.91</t>
+          <t>1.53912226310644</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>176.32</t>
+          <t>1.76317261778737</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>196.6</t>
+          <t>1.96604103278814</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>215.65</t>
+          <t>2.15653422778019</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>174.75</t>
+          <t>1.74748381675217</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>204.1</t>
+          <t>2.04100335940344</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>236.32</t>
+          <t>2.36320475722598</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>239.84</t>
+          <t>2.39842258552192</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>217.44</t>
+          <t>2.17438111001415</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>205.41</t>
+          <t>2.05414089043411</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>205.09</t>
+          <t>2.05088070163176</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>209.01</t>
+          <t>2.09011929439924</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>208.39</t>
+          <t>2.08391801908618</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>189.98</t>
+          <t>1.89979974182728</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>188.94</t>
+          <t>1.88936301241197</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>201.92</t>
+          <t>2.01916734903094</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>226.5</t>
+          <t>2.26504274392392</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>223.91</t>
+          <t>2.23908952614129</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>204.27</t>
+          <t>2.04266808781349</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>176.81</t>
+          <t>1.76812615800833</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>187.17</t>
+          <t>1.87166245793094</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>212.93</t>
+          <t>2.12929887241359</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>220.03</t>
+          <t>2.20033529079528</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>245.41</t>
+          <t>2.45414019482744</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>231.54</t>
+          <t>2.31539550958392</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>224.94</t>
+          <t>2.24937826788904</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>239.57</t>
+          <t>2.39567061121978</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>223.33</t>
+          <t>2.23328428582069</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>224.48</t>
+          <t>2.24484334297733</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>220.34</t>
+          <t>2.20335853841051</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>212.17</t>
+          <t>2.12170698101272</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>220.15</t>
+          <t>2.20147496784422</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>238.01</t>
+          <t>2.38005417416732</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>238.84</t>
+          <t>2.38835033886674</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>485.57</t>
+          <t>4.85565515775713</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>457.85</t>
+          <t>4.57846548825072</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>453.67</t>
+          <t>4.53674182390031</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>354.3</t>
+          <t>3.54296670880097</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>328.19</t>
+          <t>3.28190962727195</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>351.52</t>
+          <t>3.51516555783293</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>368.73</t>
+          <t>3.68725297164638</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>342.43</t>
+          <t>3.42432962459274</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>332.22</t>
+          <t>3.32217555662053</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>374.08</t>
+          <t>3.74076985231603</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>368.53</t>
+          <t>3.68534538817369</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>356.38</t>
+          <t>3.56375886432681</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>388.82</t>
+          <t>3.88817002367281</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>359.38</t>
+          <t>3.59376542409794</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>359.46</t>
+          <t>3.59460289863311</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>176.43</t>
+          <t>1.7643029244198</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>206.93</t>
+          <t>2.06933660589836</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>265.36</t>
+          <t>2.65361572036765</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>240.68</t>
+          <t>2.40676854417941</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>208.29</t>
+          <t>2.08285182370449</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>183.56</t>
+          <t>1.83562708865086</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>203.21</t>
+          <t>2.03211155533937</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>181.46</t>
+          <t>1.81455428160758</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>189.41</t>
+          <t>1.89408314456065</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>159.25</t>
+          <t>1.59251581327663</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>149.26</t>
+          <t>1.49257264572047</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>153.32</t>
+          <t>1.53316340294461</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>185.52</t>
+          <t>1.85515729157249</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>155.3</t>
+          <t>1.55300730800096</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>194.89</t>
+          <t>1.94892417678918</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>509.61</t>
+          <t>5.09606722609266</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>505.02</t>
+          <t>5.05020314828422</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>495.04</t>
+          <t>4.95041558920848</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>477.99</t>
+          <t>4.77990853725941</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>455.16</t>
+          <t>4.55157959685898</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>521.55</t>
+          <t>5.21551474895023</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>548.83</t>
+          <t>5.48826101868804</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>567.58</t>
+          <t>5.6757840946198</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>574.83</t>
+          <t>5.74828853286912</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>525.99</t>
+          <t>5.25994359594372</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>509.34</t>
+          <t>5.09339864292959</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>467.43</t>
+          <t>4.67434723788362</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>415.19</t>
+          <t>4.15187132643648</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>338.22</t>
+          <t>3.38222797043094</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>357.92</t>
+          <t>3.57922310208303</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>555.76</t>
+          <t>5.55760909910227</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>593.48</t>
+          <t>5.93478503671184</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>615.85</t>
+          <t>6.15848426676041</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>556.71</t>
+          <t>5.56708671389403</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>523.38</t>
+          <t>5.23375988051232</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>506.67</t>
+          <t>5.06665548476875</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>450.18</t>
+          <t>4.50176808871756</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>451.72</t>
+          <t>4.51722951447199</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>450.87</t>
+          <t>4.50866277926277</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>466.53</t>
+          <t>4.66526391599498</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>528.35</t>
+          <t>5.28350217036866</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>527.9</t>
+          <t>5.27903875554174</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>544.84</t>
+          <t>5.44841577874721</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>566.76</t>
+          <t>5.66762665671029</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>568.67</t>
+          <t>5.68669322245863</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>345.28</t>
+          <t>3.45282875801165</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>298.11</t>
+          <t>2.98114822813642</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>384.33</t>
+          <t>3.84327080989702</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>345.67</t>
+          <t>3.45665342501616</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>283.74</t>
+          <t>2.83743237454545</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>256.12</t>
+          <t>2.56124784470886</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>163.14</t>
+          <t>1.63141056773142</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>186.92</t>
+          <t>1.86915791169404</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>215.32</t>
+          <t>2.15319170535724</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>233.49</t>
+          <t>2.33487517590884</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>213.68</t>
+          <t>2.13679353342383</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>224.31</t>
+          <t>2.2430812771869</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>200.43</t>
+          <t>2.00431309726332</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>190.42</t>
+          <t>1.90422847960078</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>217.25</t>
+          <t>2.1724646894295</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>80.12</t>
+          <t>0.801169100702404</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>0.889015645017303</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>164.98</t>
+          <t>1.64982643806331</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>117.7</t>
+          <t>1.17698322147691</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>105.76</t>
+          <t>1.05755113195118</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>108.14</t>
+          <t>1.08140031767916</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>86.31</t>
+          <t>0.863067485293419</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>64.92</t>
+          <t>0.649151937548554</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>76.53</t>
+          <t>0.765300940576238</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>66.18</t>
+          <t>0.661825933134521</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>0.701041256151764</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>71.38</t>
+          <t>0.713771792450183</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>76.31</t>
+          <t>0.763115833342492</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>64.64</t>
+          <t>0.646415497177706</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>67.63</t>
+          <t>0.676323508110889</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>212.44</t>
+          <t>2.12436906007462</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>201.8</t>
+          <t>2.01804160187305</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>195.39</t>
+          <t>1.95393024979135</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>193.52</t>
+          <t>1.93524652652714</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>220.5</t>
+          <t>2.20502067557987</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>234.71</t>
+          <t>2.34707890970289</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>305.33</t>
+          <t>3.05333495924963</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>308.47</t>
+          <t>3.08474122561262</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>358.87</t>
+          <t>3.58873593283774</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>355.8</t>
+          <t>3.55797968001937</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>344.19</t>
+          <t>3.4419077537589</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>360.14</t>
+          <t>3.60138696038919</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>359.94</t>
+          <t>3.5994115681264</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>353.56</t>
+          <t>3.53556045521393</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>401.82</t>
+          <t>4.01817147716665</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>187.03</t>
+          <t>1.87033917079791</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>180.57</t>
+          <t>1.80566096214135</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>225.95</t>
+          <t>2.25945655659459</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>184.73</t>
+          <t>1.84730342740089</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>181.15</t>
+          <t>1.81149846620719</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>172.09</t>
+          <t>1.72090681359024</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>162.92</t>
+          <t>1.62915191953315</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>165.36</t>
+          <t>1.65360341888371</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>224.34</t>
+          <t>2.24344339561782</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>164.19</t>
+          <t>1.64189653168586</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>165.74</t>
+          <t>1.65740128497077</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>204.89</t>
+          <t>2.0488999541981</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>214.58</t>
+          <t>2.14580803341251</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>209.31</t>
+          <t>2.09314328791937</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>262.87</t>
+          <t>2.62869366118377</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>593.77</t>
+          <t>5.93765069732347</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>602.56</t>
+          <t>6.0256384882079</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>664.43</t>
+          <t>6.64433703418663</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>553.44</t>
+          <t>5.53438436315465</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>421.37</t>
+          <t>4.21374330497879</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>377.09</t>
+          <t>3.77090587488388</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>371.91</t>
+          <t>3.71905454932889</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>476.82</t>
+          <t>4.76820804181671</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>621.81</t>
+          <t>6.21808069582962</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>516.21</t>
+          <t>5.16212605862982</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>443.47</t>
+          <t>4.43470940634261</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>449.31</t>
+          <t>4.49306382947346</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>422.17</t>
+          <t>4.22168123175262</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>395.32</t>
+          <t>3.95318352689354</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>449.52</t>
+          <t>4.49523085222873</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>235.73</t>
+          <t>2.35732358620158</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>222.85</t>
+          <t>2.22852643060416</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>235.74</t>
+          <t>2.35742819020139</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>256.11</t>
+          <t>2.56112049372134</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>295.76</t>
+          <t>2.9575978353544</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>255.4</t>
+          <t>2.55402348636045</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>248.25</t>
+          <t>2.48248892625111</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>228.32</t>
+          <t>2.28315877262586</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>196.78</t>
+          <t>1.9677744086337</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>187.98</t>
+          <t>1.87984651167889</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>172.43</t>
+          <t>1.72427932202528</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>172.46</t>
+          <t>1.72458568020689</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>1.49495309305984</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>108.46</t>
+          <t>1.08460698328091</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>99.19</t>
+          <t>0.991877628790233</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>815.64</t>
+          <t>8.15637767860715</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>719.46</t>
+          <t>7.19464109944721</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>759.04</t>
+          <t>7.59037198238944</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>771.8</t>
+          <t>7.71799505147452</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>782.82</t>
+          <t>7.82822658909221</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>730.84</t>
+          <t>7.30844089934705</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>732.44</t>
+          <t>7.32440968899932</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>773.44</t>
+          <t>7.7343984954424</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>686.59</t>
+          <t>6.8658912284145</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>508.49</t>
+          <t>5.08493584789378</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>491.8</t>
+          <t>4.91797314397087</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>458.54</t>
+          <t>4.5854208585153</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>400.41</t>
+          <t>4.00405675010057</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>406.5</t>
+          <t>4.06498785310179</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>318.33</t>
+          <t>3.18325431489819</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>149.39</t>
+          <t>1.49386261344113</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>157.32</t>
+          <t>1.57320270242001</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>188.72</t>
+          <t>1.88719859136232</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>175.91</t>
+          <t>1.75913934381993</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>178.92</t>
+          <t>1.7891594489827</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>171.12</t>
+          <t>1.71124852416698</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>155.44</t>
+          <t>1.55443626527778</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>1.56003166484462</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>135.81</t>
+          <t>1.35807305875713</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>144.53</t>
+          <t>1.44530816031597</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>155.76</t>
+          <t>1.55756940146654</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>167.64</t>
+          <t>1.67642214520546</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>174.86</t>
+          <t>1.74857916044533</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>108.16</t>
+          <t>1.08163340573468</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>106.86</t>
+          <t>1.06860296136363</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>218.24</t>
+          <t>2.18236186486249</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>207.43</t>
+          <t>2.07425908777328</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>250.74</t>
+          <t>2.50737384515184</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>227.89</t>
+          <t>2.27888097111439</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>221.88</t>
+          <t>2.21879542396331</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>198.28</t>
+          <t>1.98276308426688</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>196.02</t>
+          <t>1.96018881682427</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>177.85</t>
+          <t>1.77850515609046</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>165.7</t>
+          <t>1.6569970587485</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>151.01</t>
+          <t>1.51013243884535</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>145.21</t>
+          <t>1.45210120043746</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>148.54</t>
+          <t>1.48538863126653</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>143.64</t>
+          <t>1.43639413662685</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>165.13</t>
+          <t>1.65132265708057</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>197.76</t>
+          <t>1.9776301089934</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>443.94</t>
+          <t>4.43941851202304</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>389.57</t>
+          <t>3.89566233721573</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>365.96</t>
+          <t>3.65963785288109</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>367.38</t>
+          <t>3.67381065614052</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>323.47</t>
+          <t>3.2347335535235</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>3.9100073911563</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>428.76</t>
+          <t>4.28759445495139</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>510.81</t>
+          <t>5.10813554109399</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>468.48</t>
+          <t>4.68478444750952</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>426.82</t>
+          <t>4.26817555291243</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>469.69</t>
+          <t>4.69694672387477</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>486.41</t>
+          <t>4.86414204409664</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>476.39</t>
+          <t>4.76392327957974</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>216.92</t>
+          <t>2.16919521353102</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>256.57</t>
+          <t>2.56565355102731</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>245.3</t>
+          <t>2.45300597960029</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>225.09</t>
+          <t>2.25091606093784</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>254.71</t>
+          <t>2.54705604945509</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>263.2</t>
+          <t>2.63197739693124</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>261.53</t>
+          <t>2.61525729485983</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>239.56</t>
+          <t>2.39558791484288</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>229.93</t>
+          <t>2.29934320816332</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>237.36</t>
+          <t>2.37364003618362</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>238.86</t>
+          <t>2.38856134961552</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>248.27</t>
+          <t>2.48274603802001</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>256.04</t>
+          <t>2.56035654807816</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>265.82</t>
+          <t>2.65815912011877</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>304.58</t>
+          <t>3.04578255160124</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>314.25</t>
+          <t>3.14245820845309</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>348.33</t>
+          <t>3.48334512161575</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>227.84</t>
+          <t>2.27836660316184</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>230.7</t>
+          <t>2.30697795650734</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>227.73</t>
+          <t>2.27729920587563</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>208.94</t>
+          <t>2.08944685555994</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>202.03</t>
+          <t>2.02029402837317</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>165.45</t>
+          <t>1.65448115484279</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>150.94</t>
+          <t>1.5094052576737</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>144.85</t>
+          <t>1.44853796094504</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>1.37735871491173</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>129.83</t>
+          <t>1.29828827456722</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>130.28</t>
+          <t>1.30282117979391</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>132.13</t>
+          <t>1.32127496377299</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>149.63</t>
+          <t>1.49627492930713</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>157.81</t>
+          <t>1.57814536578502</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>157.93</t>
+          <t>1.57931288149522</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-0.0953158457410942</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-0.05579560636414</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-0.0678401617870862</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-0.093491066349475</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>-0.133698451930783</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-0.133760894173209</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-9.66</t>
+          <t>-0.0966439641797612</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-10.1</t>
+          <t>-0.10096531324653</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-0.0316043899825678</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.0129663142355403</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.00678465647836712</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0.0228873511979857</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>0.126367761104867</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>0.19470859076616</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>0.182016776891606</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>91.88</t>
+          <t>0.918832633984032</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>97.72</t>
+          <t>0.977160857185607</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>98.92</t>
+          <t>0.989211529152815</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>94.57</t>
+          <t>0.945683298408303</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>91.35</t>
+          <t>0.913483438623916</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>0.841503316342954</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>83.14</t>
+          <t>0.831427417303781</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>0.823959192412664</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>83.98</t>
+          <t>0.839756615158129</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>0.825973966077634</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>81.83</t>
+          <t>0.818251328516197</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>82.81</t>
+          <t>0.828091022215457</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>93.14</t>
+          <t>0.931421651319746</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>97.44</t>
+          <t>0.974442819156062</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>94.88</t>
+          <t>0.948802629524249</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
